--- a/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S2_atk10pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,17 +548,17 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Não</t>
+          <t>Sim</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1418130</t>
+          <t>819994</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,12 +662,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>1983389</t>
+          <t>1163412</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2365990</t>
+          <t>1202595</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -776,12 +776,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.59</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2473137</t>
+          <t>1270559</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -833,12 +833,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2750450</t>
+          <t>1479908</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1.79</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3018543</t>
+          <t>1538652</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -952,7 +952,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.32</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>3418903</t>
+          <t>1880268</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3897996</t>
+          <t>2017746</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.19</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>4111031</t>
+          <t>2093303</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4263660</t>
+          <t>2170374</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>4377861</t>
+          <t>2207504</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4742321</t>
+          <t>2534834</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>5247684</t>
+          <t>2712868</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.95</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>5427013</t>
+          <t>2714162</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>5419188</t>
+          <t>2705043</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,17 +1460,17 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.13</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Sim</t>
+          <t>Não</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5410048</t>
+          <t>2705022</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
